--- a/tmp/exports/weakpwd_测试001_2026-05-31_2026-06-29.xlsx
+++ b/tmp/exports/weakpwd_测试001_2026-05-31_2026-06-29.xlsx
@@ -1714,17 +1714,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IMAP 弱密码</t>
+          <t>FTP 弱密码</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abc123</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
         <is>
           <t>页面url: -
 请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1812,17 +1812,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>IMAP 弱密码</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abc123</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
         <is>
           <t>页面url: -
 请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1910,12 +1910,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POP3 弱密码</t>
+          <t>LDAP 弱密码</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1982,105 +1982,197 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SMTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>admin1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abcd123</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>192.168.30.190</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Telnet 弱密码</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-06-16 13:54:33</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-06-16 13:54:33</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>192.168.30.190</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -2091,98 +2183,6 @@
 [Yes]</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LDAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2202,17 +2202,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SMTP 弱密码</t>
+          <t>POP3 弱密码</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>admin1</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abcd123</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>

--- a/tmp/exports/weakpwd_测试001_2026-05-31_2026-06-29.xlsx
+++ b/tmp/exports/weakpwd_测试001_2026-05-31_2026-06-29.xlsx
@@ -1714,12 +1714,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>LDAP 弱密码</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1786,111 +1786,105 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SMTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>admin1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>abcd123</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>192.168.30.190</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IMAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>abc123</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1910,12 +1904,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LDAP 弱密码</t>
+          <t>Telnet 弱密码</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1982,197 +1976,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SMTP 弱密码</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>abcd123</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Telnet 弱密码</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54:33</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -2183,6 +1987,202 @@
 [Yes]</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>POP3 弱密码</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>192.168.30.190</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54:33</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>192.168.30.190</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2202,17 +2202,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POP3 弱密码</t>
+          <t>IMAP 弱密码</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abc123</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
         <is>
           <t>页面url: -
 请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
